--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AI3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,6 +700,124 @@
         </is>
       </c>
       <c r="AI2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>11:10:00</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="E3" t="n">
+        <v>239632</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6315</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="I3" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>876</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1149</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>6125</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6994</v>
+      </c>
+      <c r="R3" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2508</v>
+      </c>
+      <c r="T3" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1915</v>
+      </c>
+      <c r="V3" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="W3" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI3"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,6 +818,124 @@
         </is>
       </c>
       <c r="AI3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11:12:17</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="E4" t="n">
+        <v>239746</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6309</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="I4" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>880</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1157</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>6119</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6980</v>
+      </c>
+      <c r="R4" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2496</v>
+      </c>
+      <c r="T4" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1917</v>
+      </c>
+      <c r="V4" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="W4" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -936,6 +936,124 @@
         </is>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>11:14:35</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="E5" t="n">
+        <v>239630</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6315</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="I5" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>871</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1168</v>
+      </c>
+      <c r="N5" t="n">
+        <v>11</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>6112</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>7036</v>
+      </c>
+      <c r="R5" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2486</v>
+      </c>
+      <c r="T5" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1941</v>
+      </c>
+      <c r="V5" t="n">
+        <v>32</v>
+      </c>
+      <c r="W5" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI5"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1054,6 +1054,124 @@
         </is>
       </c>
       <c r="AI5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>11:18:01</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="E6" t="n">
+        <v>239734</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6304</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="I6" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>868</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1162</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-6</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>6169</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>7057</v>
+      </c>
+      <c r="R6" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2519</v>
+      </c>
+      <c r="T6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1965</v>
+      </c>
+      <c r="V6" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="W6" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1172,6 +1172,124 @@
         </is>
       </c>
       <c r="AI6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>11:19:13</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="E7" t="n">
+        <v>239736</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6300</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="I7" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>867</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1164</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>6176</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7074</v>
+      </c>
+      <c r="R7" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2537</v>
+      </c>
+      <c r="T7" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1976</v>
+      </c>
+      <c r="V7" t="n">
+        <v>32</v>
+      </c>
+      <c r="W7" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1290,6 +1290,124 @@
         </is>
       </c>
       <c r="AI7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>11:20:22</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E8" t="n">
+        <v>239800</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6297</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="I8" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>870</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1165</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>6216</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7080</v>
+      </c>
+      <c r="R8" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2562</v>
+      </c>
+      <c r="T8" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1980</v>
+      </c>
+      <c r="V8" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="W8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1408,6 +1408,124 @@
         </is>
       </c>
       <c r="AI8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>11:23:49</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E9" t="n">
+        <v>239800</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6288</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="I9" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>870</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1168</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>6250</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7114</v>
+      </c>
+      <c r="R9" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2567</v>
+      </c>
+      <c r="T9" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2007</v>
+      </c>
+      <c r="V9" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="W9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1528,6 +1528,242 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>11:25:16</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="E10" t="n">
+        <v>239850</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6283</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-2.51</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="I10" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>873</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1166</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>6261</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7107</v>
+      </c>
+      <c r="R10" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2567</v>
+      </c>
+      <c r="T10" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2002</v>
+      </c>
+      <c r="V10" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="W10" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>11:26:42</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E11" t="n">
+        <v>239774</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6282</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-2.53</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="I11" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>872</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1164</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>6276</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7161</v>
+      </c>
+      <c r="R11" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2573</v>
+      </c>
+      <c r="T11" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2007</v>
+      </c>
+      <c r="V11" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="W11" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0/2</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI11"/>
+  <dimension ref="A1:AI12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1764,6 +1764,124 @@
       <c r="AI11" t="inlineStr">
         <is>
           <t>0/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11:27:54</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>239920</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6283</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-2.51</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="I12" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>874</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1171</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>6296</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>7169</v>
+      </c>
+      <c r="R12" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2572</v>
+      </c>
+      <c r="T12" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2006</v>
+      </c>
+      <c r="V12" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI12"/>
+  <dimension ref="A1:AI13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1880,6 +1880,124 @@
         </is>
       </c>
       <c r="AI12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>11:29:03</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="E13" t="n">
+        <v>239874</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6284</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="I13" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>873</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1167</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>6280</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>7179</v>
+      </c>
+      <c r="R13" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2551</v>
+      </c>
+      <c r="T13" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2010</v>
+      </c>
+      <c r="V13" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="W13" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI13"/>
+  <dimension ref="A1:AI14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2000,6 +2000,124 @@
       <c r="AI13" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>11:32:29</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="E14" t="n">
+        <v>239650</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6301</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="I14" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>880</v>
+      </c>
+      <c r="K14" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1163</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>6271</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>7177</v>
+      </c>
+      <c r="R14" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2539</v>
+      </c>
+      <c r="T14" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1998</v>
+      </c>
+      <c r="V14" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>1/1</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI14"/>
+  <dimension ref="A1:AI15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2118,6 +2118,124 @@
       <c r="AI14" t="inlineStr">
         <is>
           <t>1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>11:34:46</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>239695</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6289</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-2.42</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="I15" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>876</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1172</v>
+      </c>
+      <c r="N15" t="n">
+        <v>9</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>6325</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>7176</v>
+      </c>
+      <c r="R15" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2572</v>
+      </c>
+      <c r="T15" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1963</v>
+      </c>
+      <c r="V15" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI15"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2234,6 +2234,124 @@
         </is>
       </c>
       <c r="AI15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>11:35:54</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="E16" t="n">
+        <v>239713</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6290</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="I16" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>862</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-14</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1173</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>6337</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>7251</v>
+      </c>
+      <c r="R16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2584</v>
+      </c>
+      <c r="T16" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1964</v>
+      </c>
+      <c r="V16" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI16"/>
+  <dimension ref="A1:AI17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2352,6 +2352,124 @@
         </is>
       </c>
       <c r="AI16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>11:37:04</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="E17" t="n">
+        <v>239744</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6288</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="I17" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>857</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1178</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>6357</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7286</v>
+      </c>
+      <c r="R17" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2601</v>
+      </c>
+      <c r="T17" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1992</v>
+      </c>
+      <c r="V17" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI17"/>
+  <dimension ref="A1:AI18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2470,6 +2470,124 @@
         </is>
       </c>
       <c r="AI17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>11:39:23</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="E18" t="n">
+        <v>239986</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6287</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="I18" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>874</v>
+      </c>
+      <c r="K18" t="n">
+        <v>17</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1172</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-6</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>6446</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>7359</v>
+      </c>
+      <c r="R18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2612</v>
+      </c>
+      <c r="T18" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2042</v>
+      </c>
+      <c r="V18" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="W18" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI18"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2588,6 +2588,124 @@
         </is>
       </c>
       <c r="AI18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>11:40:32</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="E19" t="n">
+        <v>240067</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6287</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="I19" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J19" t="n">
+        <v>882</v>
+      </c>
+      <c r="K19" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1172</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>6480</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>7369</v>
+      </c>
+      <c r="R19" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2610</v>
+      </c>
+      <c r="T19" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2044</v>
+      </c>
+      <c r="V19" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI19"/>
+  <dimension ref="A1:AI20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2706,6 +2706,124 @@
         </is>
       </c>
       <c r="AI19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>11:41:40</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="E20" t="n">
+        <v>240097</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6286</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="I20" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>887</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1172</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>6502</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7393</v>
+      </c>
+      <c r="R20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2612</v>
+      </c>
+      <c r="T20" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2053</v>
+      </c>
+      <c r="V20" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI20"/>
+  <dimension ref="A1:AI21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2824,6 +2824,118 @@
         </is>
       </c>
       <c r="AI20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>11:42:06</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="E21" t="n">
+        <v>246999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6721</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="I21" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>888</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1173</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>6501</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>7394</v>
+      </c>
+      <c r="R21" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2608</v>
+      </c>
+      <c r="T21" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2053</v>
+      </c>
+      <c r="V21" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="W21" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI21"/>
+  <dimension ref="A1:AI22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2936,6 +2936,124 @@
         </is>
       </c>
       <c r="AI21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>11:44:23</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E22" t="n">
+        <v>246943</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6728</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="I22" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J22" t="n">
+        <v>888</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1173</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>6535</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>7438</v>
+      </c>
+      <c r="R22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2619</v>
+      </c>
+      <c r="T22" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2068</v>
+      </c>
+      <c r="V22" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="W22" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI22"/>
+  <dimension ref="A1:AI23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3054,6 +3054,124 @@
         </is>
       </c>
       <c r="AI22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>11:45:38</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="E23" t="n">
+        <v>247050</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6726</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="I23" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>901</v>
+      </c>
+      <c r="K23" t="n">
+        <v>13</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1176</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>6562</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>7413</v>
+      </c>
+      <c r="R23" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2615</v>
+      </c>
+      <c r="T23" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2076</v>
+      </c>
+      <c r="V23" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI23"/>
+  <dimension ref="A1:AI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3174,6 +3174,124 @@
       <c r="AI23" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>11:46:54</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="E24" t="n">
+        <v>247212</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6727</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="I24" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J24" t="n">
+        <v>918</v>
+      </c>
+      <c r="K24" t="n">
+        <v>17</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1171</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>6599</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>7376</v>
+      </c>
+      <c r="R24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2599</v>
+      </c>
+      <c r="T24" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2070</v>
+      </c>
+      <c r="V24" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="W24" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI24"/>
+  <dimension ref="A1:AI25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3290,6 +3290,124 @@
         </is>
       </c>
       <c r="AI24" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>11:48:08</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="E25" t="n">
+        <v>247384</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6732</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="I25" t="n">
+        <v>241000</v>
+      </c>
+      <c r="J25" t="n">
+        <v>24</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-894</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>141</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1030</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>4001</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>6938</v>
+      </c>
+      <c r="R25" t="n">
+        <v>235000</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="T25" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2010</v>
+      </c>
+      <c r="V25" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="W25" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>235000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
         <is>
           <t>0/4</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI25"/>
+  <dimension ref="A1:AI26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3410,6 +3410,118 @@
       <c r="AI25" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>11:50:03</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="E26" t="n">
+        <v>240316</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6331</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="I26" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J26" t="n">
+        <v>937</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>1104</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>6604</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>7345</v>
+      </c>
+      <c r="R26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2548</v>
+      </c>
+      <c r="T26" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2041</v>
+      </c>
+      <c r="V26" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="W26" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI26"/>
+  <dimension ref="A1:AI27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3522,6 +3522,124 @@
       <c r="AI26" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>11:54:00</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E27" t="n">
+        <v>240529</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6335</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="I27" t="n">
+        <v>241000</v>
+      </c>
+      <c r="J27" t="n">
+        <v>23</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-914</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>150</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-954</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>4094</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>7094</v>
+      </c>
+      <c r="R27" t="n">
+        <v>235000</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1133</v>
+      </c>
+      <c r="T27" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2033</v>
+      </c>
+      <c r="V27" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W27" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>235000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI27"/>
+  <dimension ref="A1:AI28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3640,6 +3640,124 @@
       <c r="AI27" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>11:56:32</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E28" t="n">
+        <v>240388</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6336</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="I28" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1008</v>
+      </c>
+      <c r="K28" t="n">
+        <v>985</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1091</v>
+      </c>
+      <c r="N28" t="n">
+        <v>941</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>6695</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>7476</v>
+      </c>
+      <c r="R28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2556</v>
+      </c>
+      <c r="T28" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2048</v>
+      </c>
+      <c r="V28" t="n">
+        <v>31</v>
+      </c>
+      <c r="W28" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>1/1</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI28"/>
+  <dimension ref="A1:AI29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3758,6 +3758,124 @@
       <c r="AI28" t="inlineStr">
         <is>
           <t>1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>11:59:05</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E29" t="n">
+        <v>240775</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6330</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="I29" t="n">
+        <v>241000</v>
+      </c>
+      <c r="J29" t="n">
+        <v>23</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-985</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>154</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-937</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>4220</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>7070</v>
+      </c>
+      <c r="R29" t="n">
+        <v>235000</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1108</v>
+      </c>
+      <c r="T29" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2041</v>
+      </c>
+      <c r="V29" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="W29" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>235000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI29"/>
+  <dimension ref="A1:AI30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3876,6 +3876,124 @@
       <c r="AI29" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>12:01:41</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E30" t="n">
+        <v>240770</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6315</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="I30" t="n">
+        <v>241000</v>
+      </c>
+      <c r="J30" t="n">
+        <v>24</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>164</v>
+      </c>
+      <c r="N30" t="n">
+        <v>10</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>4274</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>7066</v>
+      </c>
+      <c r="R30" t="n">
+        <v>235000</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1094</v>
+      </c>
+      <c r="T30" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2050</v>
+      </c>
+      <c r="V30" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="W30" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>235000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>0/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI30"/>
+  <dimension ref="A1:AI31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3994,6 +3994,124 @@
       <c r="AI30" t="inlineStr">
         <is>
           <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>12:05:29</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E31" t="n">
+        <v>240555</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6318</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="I31" t="n">
+        <v>241000</v>
+      </c>
+      <c r="J31" t="n">
+        <v>24</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>148</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-16</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>4301</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>7193</v>
+      </c>
+      <c r="R31" t="n">
+        <v>235000</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1097</v>
+      </c>
+      <c r="T31" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2117</v>
+      </c>
+      <c r="V31" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>235000</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Bearish (Strong)</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>1/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI31"/>
+  <dimension ref="A1:AI32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4112,6 +4112,124 @@
       <c r="AI31" t="inlineStr">
         <is>
           <t>1/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>12:08:02</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E32" t="n">
+        <v>240588</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6318</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="I32" t="n">
+        <v>241000</v>
+      </c>
+      <c r="J32" t="n">
+        <v>23</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>151</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>4292</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>7218</v>
+      </c>
+      <c r="R32" t="n">
+        <v>235000</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1094</v>
+      </c>
+      <c r="T32" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2120</v>
+      </c>
+      <c r="V32" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>235000</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Bearish (Strong)</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>0/2</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI32"/>
+  <dimension ref="A1:AI33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4228,6 +4228,124 @@
         </is>
       </c>
       <c r="AI32" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>12:10:31</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E33" t="n">
+        <v>240500</v>
+      </c>
+      <c r="F33" t="n">
+        <v>6317</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="I33" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1060</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1037</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>1074</v>
+      </c>
+      <c r="N33" t="n">
+        <v>923</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>6907</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>7604</v>
+      </c>
+      <c r="R33" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2594</v>
+      </c>
+      <c r="T33" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2139</v>
+      </c>
+      <c r="V33" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="W33" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
         <is>
           <t>0/2</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI33"/>
+  <dimension ref="A1:AI34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4348,6 +4348,124 @@
       <c r="AI33" t="inlineStr">
         <is>
           <t>0/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>12:11:50</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E34" t="n">
+        <v>240523</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6314</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="I34" t="n">
+        <v>241000</v>
+      </c>
+      <c r="J34" t="n">
+        <v>21</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-1039</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>158</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-916</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>4335</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>7278</v>
+      </c>
+      <c r="R34" t="n">
+        <v>235000</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1123</v>
+      </c>
+      <c r="T34" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2144</v>
+      </c>
+      <c r="V34" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="W34" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>235000</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>Bearish (Strong)</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>1/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI34"/>
+  <dimension ref="A1:AI35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4466,6 +4466,124 @@
       <c r="AI34" t="inlineStr">
         <is>
           <t>1/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>12:13:07</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E35" t="n">
+        <v>240693</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6312</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="I35" t="n">
+        <v>241000</v>
+      </c>
+      <c r="J35" t="n">
+        <v>21</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>162</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>4340</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>7263</v>
+      </c>
+      <c r="R35" t="n">
+        <v>235000</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1126</v>
+      </c>
+      <c r="T35" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2149</v>
+      </c>
+      <c r="V35" t="n">
+        <v>32</v>
+      </c>
+      <c r="W35" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>235000</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>Bearish (Strong)</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>0/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI35"/>
+  <dimension ref="A1:AI36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4584,6 +4584,124 @@
       <c r="AI35" t="inlineStr">
         <is>
           <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>12:15:45</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E36" t="n">
+        <v>240984</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6309</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="I36" t="n">
+        <v>241000</v>
+      </c>
+      <c r="J36" t="n">
+        <v>21</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>158</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>4383</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>7252</v>
+      </c>
+      <c r="R36" t="n">
+        <v>235000</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1133</v>
+      </c>
+      <c r="T36" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2154</v>
+      </c>
+      <c r="V36" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="W36" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>235000</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI36"/>
+  <dimension ref="A1:AI37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4700,6 +4700,124 @@
         </is>
       </c>
       <c r="AI36" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>12:18:20</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E37" t="n">
+        <v>241543</v>
+      </c>
+      <c r="F37" t="n">
+        <v>6310</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="I37" t="n">
+        <v>242000</v>
+      </c>
+      <c r="J37" t="n">
+        <v>66</v>
+      </c>
+      <c r="K37" t="n">
+        <v>45</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>328</v>
+      </c>
+      <c r="N37" t="n">
+        <v>170</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>4426</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>7003</v>
+      </c>
+      <c r="R37" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1124</v>
+      </c>
+      <c r="T37" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2048</v>
+      </c>
+      <c r="V37" t="n">
+        <v>32</v>
+      </c>
+      <c r="W37" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
         <is>
           <t>0/4</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI37"/>
+  <dimension ref="A1:AI38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4820,6 +4820,124 @@
       <c r="AI37" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>12:20:52</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E38" t="n">
+        <v>241531</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6308</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="I38" t="n">
+        <v>242000</v>
+      </c>
+      <c r="J38" t="n">
+        <v>79</v>
+      </c>
+      <c r="K38" t="n">
+        <v>13</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>312</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-16</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>4531</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>6810</v>
+      </c>
+      <c r="R38" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1174</v>
+      </c>
+      <c r="T38" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1945</v>
+      </c>
+      <c r="V38" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="W38" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>0/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI38"/>
+  <dimension ref="A1:AI39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4936,6 +4936,124 @@
         </is>
       </c>
       <c r="AI38" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>12:26:08</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E39" t="n">
+        <v>242496</v>
+      </c>
+      <c r="F39" t="n">
+        <v>6347</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="I39" t="n">
+        <v>242000</v>
+      </c>
+      <c r="J39" t="n">
+        <v>126</v>
+      </c>
+      <c r="K39" t="n">
+        <v>47</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>283</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-29</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>5117</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>6797</v>
+      </c>
+      <c r="R39" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1341</v>
+      </c>
+      <c r="T39" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1917</v>
+      </c>
+      <c r="V39" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
         <is>
           <t>0/3</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI39"/>
+  <dimension ref="A1:AI40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5056,6 +5056,124 @@
       <c r="AI39" t="inlineStr">
         <is>
           <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>12:29:59</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E40" t="n">
+        <v>242702</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6329</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="I40" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J40" t="n">
+        <v>18</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-108</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>315</v>
+      </c>
+      <c r="N40" t="n">
+        <v>32</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>5292</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>6726</v>
+      </c>
+      <c r="R40" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1411</v>
+      </c>
+      <c r="T40" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1906</v>
+      </c>
+      <c r="V40" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="W40" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI40"/>
+  <dimension ref="A1:AI41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5174,6 +5174,124 @@
       <c r="AI40" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>12:31:19</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E41" t="n">
+        <v>242500</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6334</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="I41" t="n">
+        <v>242000</v>
+      </c>
+      <c r="J41" t="n">
+        <v>226</v>
+      </c>
+      <c r="K41" t="n">
+        <v>208</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>242</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-73</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>5603</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>6759</v>
+      </c>
+      <c r="R41" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1449</v>
+      </c>
+      <c r="T41" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1926</v>
+      </c>
+      <c r="V41" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="W41" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>0/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI41"/>
+  <dimension ref="A1:AI42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5290,6 +5290,124 @@
         </is>
       </c>
       <c r="AI41" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>12:32:37</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E42" t="n">
+        <v>242660</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6368</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="I42" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J42" t="n">
+        <v>30</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-196</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>317</v>
+      </c>
+      <c r="N42" t="n">
+        <v>75</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>5517</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>6789</v>
+      </c>
+      <c r="R42" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1457</v>
+      </c>
+      <c r="T42" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1928</v>
+      </c>
+      <c r="V42" t="n">
+        <v>32</v>
+      </c>
+      <c r="W42" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
         <is>
           <t>0/3</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI42"/>
+  <dimension ref="A1:AI43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5408,6 +5408,124 @@
         </is>
       </c>
       <c r="AI42" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>12:33:53</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E43" t="n">
+        <v>242982</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6356</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="I43" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J43" t="n">
+        <v>30</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>281</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-36</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>5596</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>6801</v>
+      </c>
+      <c r="R43" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1471</v>
+      </c>
+      <c r="T43" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1912</v>
+      </c>
+      <c r="V43" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="W43" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
         <is>
           <t>0/3</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI43"/>
+  <dimension ref="A1:AI44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5528,6 +5528,124 @@
       <c r="AI43" t="inlineStr">
         <is>
           <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>12:36:20</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E44" t="n">
+        <v>242789</v>
+      </c>
+      <c r="F44" t="n">
+        <v>6412</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="I44" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J44" t="n">
+        <v>38</v>
+      </c>
+      <c r="K44" t="n">
+        <v>8</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>299</v>
+      </c>
+      <c r="N44" t="n">
+        <v>18</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>5719</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>6856</v>
+      </c>
+      <c r="R44" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1473</v>
+      </c>
+      <c r="T44" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1967</v>
+      </c>
+      <c r="V44" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="W44" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>0/2</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI44"/>
+  <dimension ref="A1:AI45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5646,6 +5646,118 @@
       <c r="AI44" t="inlineStr">
         <is>
           <t>0/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>12:39:15</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E45" t="n">
+        <v>249551</v>
+      </c>
+      <c r="F45" t="n">
+        <v>6974</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="I45" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J45" t="n">
+        <v>33</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>307</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>5754</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>7053</v>
+      </c>
+      <c r="R45" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1458</v>
+      </c>
+      <c r="T45" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2035</v>
+      </c>
+      <c r="V45" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="W45" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI45"/>
+  <dimension ref="A1:AI46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5756,6 +5756,124 @@
         </is>
       </c>
       <c r="AI45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>12:40:31</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E46" t="n">
+        <v>249645</v>
+      </c>
+      <c r="F46" t="n">
+        <v>6987</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="I46" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J46" t="n">
+        <v>31</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>308</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>5757</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>7116</v>
+      </c>
+      <c r="R46" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1457</v>
+      </c>
+      <c r="T46" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2065</v>
+      </c>
+      <c r="V46" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="W46" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI46"/>
+  <dimension ref="A1:AI47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5874,6 +5874,124 @@
         </is>
       </c>
       <c r="AI46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>12:41:46</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E47" t="n">
+        <v>249694</v>
+      </c>
+      <c r="F47" t="n">
+        <v>7031</v>
+      </c>
+      <c r="G47" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="I47" t="n">
+        <v>242000</v>
+      </c>
+      <c r="J47" t="n">
+        <v>311</v>
+      </c>
+      <c r="K47" t="n">
+        <v>280</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>265</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-43</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>5959</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>7160</v>
+      </c>
+      <c r="R47" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1476</v>
+      </c>
+      <c r="T47" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2145</v>
+      </c>
+      <c r="V47" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="W47" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI47"/>
+  <dimension ref="A1:AI48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5994,6 +5994,124 @@
       <c r="AI47" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>12:43:10</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E48" t="n">
+        <v>249891</v>
+      </c>
+      <c r="F48" t="n">
+        <v>7032</v>
+      </c>
+      <c r="G48" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="I48" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J48" t="n">
+        <v>36</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-275</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>301</v>
+      </c>
+      <c r="N48" t="n">
+        <v>36</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>5878</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>7148</v>
+      </c>
+      <c r="R48" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1509</v>
+      </c>
+      <c r="T48" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2158</v>
+      </c>
+      <c r="V48" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="W48" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI48"/>
+  <dimension ref="A1:AI49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6112,6 +6112,124 @@
       <c r="AI48" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>12:44:28</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E49" t="n">
+        <v>250200</v>
+      </c>
+      <c r="F49" t="n">
+        <v>7037</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="I49" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J49" t="n">
+        <v>39</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>304</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>5932</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>7037</v>
+      </c>
+      <c r="R49" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1534</v>
+      </c>
+      <c r="T49" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2166</v>
+      </c>
+      <c r="V49" t="n">
+        <v>33</v>
+      </c>
+      <c r="W49" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI49"/>
+  <dimension ref="A1:AI50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6228,6 +6228,124 @@
         </is>
       </c>
       <c r="AI49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>12:45:46</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E50" t="n">
+        <v>250050</v>
+      </c>
+      <c r="F50" t="n">
+        <v>7036</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I50" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J50" t="n">
+        <v>39</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>295</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-9</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>5955</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>7090</v>
+      </c>
+      <c r="R50" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1533</v>
+      </c>
+      <c r="T50" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2161</v>
+      </c>
+      <c r="V50" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="W50" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI50"/>
+  <dimension ref="A1:AI51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6346,6 +6346,124 @@
         </is>
       </c>
       <c r="AI50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>12:47:04</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E51" t="n">
+        <v>249884</v>
+      </c>
+      <c r="F51" t="n">
+        <v>7042</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I51" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J51" t="n">
+        <v>38</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>300</v>
+      </c>
+      <c r="N51" t="n">
+        <v>5</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>6056</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>7124</v>
+      </c>
+      <c r="R51" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1592</v>
+      </c>
+      <c r="T51" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2207</v>
+      </c>
+      <c r="V51" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="W51" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI51"/>
+  <dimension ref="A1:AI52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6466,6 +6466,124 @@
       <c r="AI51" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>12:50:56</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E52" t="n">
+        <v>250652</v>
+      </c>
+      <c r="F52" t="n">
+        <v>7070</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="I52" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J52" t="n">
+        <v>45</v>
+      </c>
+      <c r="K52" t="n">
+        <v>7</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>280</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-20</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>6329</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>6937</v>
+      </c>
+      <c r="R52" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1647</v>
+      </c>
+      <c r="T52" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2276</v>
+      </c>
+      <c r="V52" t="n">
+        <v>35</v>
+      </c>
+      <c r="W52" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI52"/>
+  <dimension ref="A1:AI53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6584,6 +6584,124 @@
       <c r="AI52" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>12:53:26</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E53" t="n">
+        <v>250800</v>
+      </c>
+      <c r="F53" t="n">
+        <v>7088</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="I53" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J53" t="n">
+        <v>23</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-22</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>296</v>
+      </c>
+      <c r="N53" t="n">
+        <v>16</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>6276</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>6933</v>
+      </c>
+      <c r="R53" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1690</v>
+      </c>
+      <c r="T53" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2260</v>
+      </c>
+      <c r="V53" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="W53" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>0/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI53"/>
+  <dimension ref="A1:AI54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6700,6 +6700,124 @@
         </is>
       </c>
       <c r="AI53" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>12:56:02</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E54" t="n">
+        <v>250891</v>
+      </c>
+      <c r="F54" t="n">
+        <v>7128</v>
+      </c>
+      <c r="G54" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="I54" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J54" t="n">
+        <v>22</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>302</v>
+      </c>
+      <c r="N54" t="n">
+        <v>6</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>6442</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>6934</v>
+      </c>
+      <c r="R54" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1721</v>
+      </c>
+      <c r="T54" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2286</v>
+      </c>
+      <c r="V54" t="n">
+        <v>34</v>
+      </c>
+      <c r="W54" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>241000</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
         <is>
           <t>0/3</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI54"/>
+  <dimension ref="A1:AI55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6818,6 +6818,124 @@
         </is>
       </c>
       <c r="AI54" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>12:57:19</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E55" t="n">
+        <v>250953</v>
+      </c>
+      <c r="F55" t="n">
+        <v>7149</v>
+      </c>
+      <c r="G55" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="I55" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J55" t="n">
+        <v>22</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>300</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>6491</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>6889</v>
+      </c>
+      <c r="R55" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1723</v>
+      </c>
+      <c r="T55" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2258</v>
+      </c>
+      <c r="V55" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="W55" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>241000</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
         <is>
           <t>0/3</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI55"/>
+  <dimension ref="A1:AI56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6938,6 +6938,124 @@
       <c r="AI55" t="inlineStr">
         <is>
           <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>12:58:36</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E56" t="n">
+        <v>250760</v>
+      </c>
+      <c r="F56" t="n">
+        <v>7149</v>
+      </c>
+      <c r="G56" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="I56" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J56" t="n">
+        <v>22</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>303</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>6522</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>6858</v>
+      </c>
+      <c r="R56" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1713</v>
+      </c>
+      <c r="T56" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2239</v>
+      </c>
+      <c r="V56" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="W56" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>241000</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>0/2</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI56"/>
+  <dimension ref="A1:AI57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7056,6 +7056,118 @@
       <c r="AI56" t="inlineStr">
         <is>
           <t>0/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>13:16:56</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E57" t="n">
+        <v>251185</v>
+      </c>
+      <c r="F57" t="n">
+        <v>7203</v>
+      </c>
+      <c r="G57" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.066</v>
+      </c>
+      <c r="I57" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J57" t="n">
+        <v>57</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>266</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>7006</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>6570</v>
+      </c>
+      <c r="R57" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1711</v>
+      </c>
+      <c r="T57" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2201</v>
+      </c>
+      <c r="V57" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="W57" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>242000</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI57"/>
+  <dimension ref="A1:AI58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7166,6 +7166,124 @@
         </is>
       </c>
       <c r="AI57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>13:18:13</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E58" t="n">
+        <v>251155</v>
+      </c>
+      <c r="F58" t="n">
+        <v>7208</v>
+      </c>
+      <c r="G58" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.058</v>
+      </c>
+      <c r="I58" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J58" t="n">
+        <v>65</v>
+      </c>
+      <c r="K58" t="n">
+        <v>8</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>265</v>
+      </c>
+      <c r="N58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>7038</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>6653</v>
+      </c>
+      <c r="R58" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1701</v>
+      </c>
+      <c r="T58" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2239</v>
+      </c>
+      <c r="V58" t="n">
+        <v>36</v>
+      </c>
+      <c r="W58" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>242000</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI58"/>
+  <dimension ref="A1:AI59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7284,6 +7284,124 @@
         </is>
       </c>
       <c r="AI58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>13:19:33</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E59" t="n">
+        <v>251249</v>
+      </c>
+      <c r="F59" t="n">
+        <v>7210</v>
+      </c>
+      <c r="G59" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="I59" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J59" t="n">
+        <v>66</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>262</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>7074</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>6608</v>
+      </c>
+      <c r="R59" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1700</v>
+      </c>
+      <c r="T59" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2216</v>
+      </c>
+      <c r="V59" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="W59" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>242000</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI59"/>
+  <dimension ref="A1:AI60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7402,6 +7402,118 @@
         </is>
       </c>
       <c r="AI59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>16:22:26</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E60" t="n">
+        <v>250550</v>
+      </c>
+      <c r="F60" t="n">
+        <v>7428</v>
+      </c>
+      <c r="G60" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="I60" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J60" t="n">
+        <v>484</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>249</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>10712</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>9751</v>
+      </c>
+      <c r="R60" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S60" t="n">
+        <v>2099</v>
+      </c>
+      <c r="T60" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2950</v>
+      </c>
+      <c r="V60" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="W60" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI60"/>
+  <dimension ref="A1:AI61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7514,6 +7514,118 @@
         </is>
       </c>
       <c r="AI60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>16:23:21</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E61" t="n">
+        <v>250500</v>
+      </c>
+      <c r="F61" t="n">
+        <v>7442</v>
+      </c>
+      <c r="G61" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="I61" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J61" t="n">
+        <v>484</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>249</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>10808</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>9851</v>
+      </c>
+      <c r="R61" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2123</v>
+      </c>
+      <c r="T61" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2928</v>
+      </c>
+      <c r="V61" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="W61" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI61"/>
+  <dimension ref="A1:AI62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7626,6 +7626,124 @@
         </is>
       </c>
       <c r="AI61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>16:24:26</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E62" t="n">
+        <v>250520</v>
+      </c>
+      <c r="F62" t="n">
+        <v>7445</v>
+      </c>
+      <c r="G62" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="I62" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J62" t="n">
+        <v>499</v>
+      </c>
+      <c r="K62" t="n">
+        <v>15</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>255</v>
+      </c>
+      <c r="N62" t="n">
+        <v>6</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>11034</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>9777</v>
+      </c>
+      <c r="R62" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S62" t="n">
+        <v>2152</v>
+      </c>
+      <c r="T62" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2920</v>
+      </c>
+      <c r="V62" t="n">
+        <v>27</v>
+      </c>
+      <c r="W62" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI62"/>
+  <dimension ref="A1:AI63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7744,6 +7744,124 @@
         </is>
       </c>
       <c r="AI62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>16:25:35</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E63" t="n">
+        <v>250632</v>
+      </c>
+      <c r="F63" t="n">
+        <v>7452</v>
+      </c>
+      <c r="G63" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="I63" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J63" t="n">
+        <v>321</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-178</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>625</v>
+      </c>
+      <c r="N63" t="n">
+        <v>370</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>10499</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>9525</v>
+      </c>
+      <c r="R63" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S63" t="n">
+        <v>2226</v>
+      </c>
+      <c r="T63" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2772</v>
+      </c>
+      <c r="V63" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="W63" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI63"/>
+  <dimension ref="A1:AI64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7862,6 +7862,118 @@
         </is>
       </c>
       <c r="AI63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>16:26:48</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E64" t="n">
+        <v>243458</v>
+      </c>
+      <c r="F64" t="n">
+        <v>6437</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="I64" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J64" t="n">
+        <v>482</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>270</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>11248</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>9657</v>
+      </c>
+      <c r="R64" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S64" t="n">
+        <v>2257</v>
+      </c>
+      <c r="T64" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2839</v>
+      </c>
+      <c r="V64" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI64"/>
+  <dimension ref="A1:AI65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7974,6 +7974,124 @@
         </is>
       </c>
       <c r="AI64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>16:27:57</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E65" t="n">
+        <v>243498</v>
+      </c>
+      <c r="F65" t="n">
+        <v>6440</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I65" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J65" t="n">
+        <v>494</v>
+      </c>
+      <c r="K65" t="n">
+        <v>12</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>283</v>
+      </c>
+      <c r="N65" t="n">
+        <v>13</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>11215</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>9834</v>
+      </c>
+      <c r="R65" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S65" t="n">
+        <v>2191</v>
+      </c>
+      <c r="T65" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2880</v>
+      </c>
+      <c r="V65" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="W65" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI65"/>
+  <dimension ref="A1:AI66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8092,6 +8092,124 @@
         </is>
       </c>
       <c r="AI65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>16:29:06</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E66" t="n">
+        <v>243401</v>
+      </c>
+      <c r="F66" t="n">
+        <v>6439</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="I66" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J66" t="n">
+        <v>502</v>
+      </c>
+      <c r="K66" t="n">
+        <v>8</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>281</v>
+      </c>
+      <c r="N66" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>11334</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>9872</v>
+      </c>
+      <c r="R66" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S66" t="n">
+        <v>2222</v>
+      </c>
+      <c r="T66" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2870</v>
+      </c>
+      <c r="V66" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="W66" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI66"/>
+  <dimension ref="A1:AI67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8210,6 +8210,124 @@
         </is>
       </c>
       <c r="AI66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>16:30:16</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E67" t="n">
+        <v>243520</v>
+      </c>
+      <c r="F67" t="n">
+        <v>6439</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.093</v>
+      </c>
+      <c r="I67" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J67" t="n">
+        <v>322</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-180</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>794</v>
+      </c>
+      <c r="N67" t="n">
+        <v>513</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>10810</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>9892</v>
+      </c>
+      <c r="R67" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S67" t="n">
+        <v>2278</v>
+      </c>
+      <c r="T67" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2855</v>
+      </c>
+      <c r="V67" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="W67" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI67"/>
+  <dimension ref="A1:AI68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8328,6 +8328,124 @@
         </is>
       </c>
       <c r="AI67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>16:31:26</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E68" t="n">
+        <v>243393</v>
+      </c>
+      <c r="F68" t="n">
+        <v>6440</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1.138</v>
+      </c>
+      <c r="I68" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J68" t="n">
+        <v>499</v>
+      </c>
+      <c r="K68" t="n">
+        <v>177</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>279</v>
+      </c>
+      <c r="N68" t="n">
+        <v>-515</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>11354</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>9980</v>
+      </c>
+      <c r="R68" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S68" t="n">
+        <v>2256</v>
+      </c>
+      <c r="T68" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2832</v>
+      </c>
+      <c r="V68" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="W68" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI68"/>
+  <dimension ref="A1:AI69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8448,6 +8448,124 @@
       <c r="AI68" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>16:32:38</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E69" t="n">
+        <v>243363</v>
+      </c>
+      <c r="F69" t="n">
+        <v>6439</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1.124</v>
+      </c>
+      <c r="I69" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J69" t="n">
+        <v>479</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>291</v>
+      </c>
+      <c r="N69" t="n">
+        <v>12</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>11285</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>10043</v>
+      </c>
+      <c r="R69" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S69" t="n">
+        <v>2215</v>
+      </c>
+      <c r="T69" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2831</v>
+      </c>
+      <c r="V69" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="W69" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>0/1</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI69"/>
+  <dimension ref="A1:AI70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8566,6 +8566,124 @@
       <c r="AI69" t="inlineStr">
         <is>
           <t>0/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>16:33:50</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>243300</v>
+      </c>
+      <c r="F70" t="n">
+        <v>6441</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="I70" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J70" t="n">
+        <v>502</v>
+      </c>
+      <c r="K70" t="n">
+        <v>23</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>297</v>
+      </c>
+      <c r="N70" t="n">
+        <v>6</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>11225</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>10107</v>
+      </c>
+      <c r="R70" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S70" t="n">
+        <v>2181</v>
+      </c>
+      <c r="T70" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2813</v>
+      </c>
+      <c r="V70" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="W70" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>0/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI70"/>
+  <dimension ref="A1:AI71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8684,6 +8684,124 @@
       <c r="AI70" t="inlineStr">
         <is>
           <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>16:35:03</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>243300</v>
+      </c>
+      <c r="F71" t="n">
+        <v>6441</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="I71" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J71" t="n">
+        <v>514</v>
+      </c>
+      <c r="K71" t="n">
+        <v>12</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>305</v>
+      </c>
+      <c r="N71" t="n">
+        <v>8</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>11423</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>9928</v>
+      </c>
+      <c r="R71" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S71" t="n">
+        <v>2217</v>
+      </c>
+      <c r="T71" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2756</v>
+      </c>
+      <c r="V71" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="W71" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI71"/>
+  <dimension ref="A1:AI72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8802,6 +8802,124 @@
       <c r="AI71" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>16:36:16</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E72" t="n">
+        <v>243521</v>
+      </c>
+      <c r="F72" t="n">
+        <v>6432</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="I72" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J72" t="n">
+        <v>312</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-202</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>894</v>
+      </c>
+      <c r="N72" t="n">
+        <v>589</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>10802</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>9875</v>
+      </c>
+      <c r="R72" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S72" t="n">
+        <v>2217</v>
+      </c>
+      <c r="T72" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2738</v>
+      </c>
+      <c r="V72" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="W72" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI72"/>
+  <dimension ref="A1:AI73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8920,6 +8920,124 @@
       <c r="AI72" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>16:38:39</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E73" t="n">
+        <v>243456</v>
+      </c>
+      <c r="F73" t="n">
+        <v>6428</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I73" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J73" t="n">
+        <v>540</v>
+      </c>
+      <c r="K73" t="n">
+        <v>228</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>304</v>
+      </c>
+      <c r="N73" t="n">
+        <v>-590</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>11495</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>9992</v>
+      </c>
+      <c r="R73" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S73" t="n">
+        <v>2177</v>
+      </c>
+      <c r="T73" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2804</v>
+      </c>
+      <c r="V73" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="W73" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>1/1</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI73"/>
+  <dimension ref="A1:AI74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9038,6 +9038,124 @@
       <c r="AI73" t="inlineStr">
         <is>
           <t>1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>16:39:54</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>243294</v>
+      </c>
+      <c r="F74" t="n">
+        <v>6428</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1.124</v>
+      </c>
+      <c r="I74" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J74" t="n">
+        <v>510</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-30</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>305</v>
+      </c>
+      <c r="N74" t="n">
+        <v>1</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>11386</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>10130</v>
+      </c>
+      <c r="R74" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S74" t="n">
+        <v>2147</v>
+      </c>
+      <c r="T74" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2785</v>
+      </c>
+      <c r="V74" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="W74" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>0/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI74"/>
+  <dimension ref="A1:AI75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9156,6 +9156,124 @@
       <c r="AI74" t="inlineStr">
         <is>
           <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>16:41:07</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E75" t="n">
+        <v>243240</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6428</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="I75" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J75" t="n">
+        <v>513</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>305</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>11464</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>10069</v>
+      </c>
+      <c r="R75" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S75" t="n">
+        <v>2142</v>
+      </c>
+      <c r="T75" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2765</v>
+      </c>
+      <c r="V75" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="W75" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI75"/>
+  <dimension ref="A1:AI76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9274,6 +9274,124 @@
       <c r="AI75" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>16:42:22</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E76" t="n">
+        <v>243396</v>
+      </c>
+      <c r="F76" t="n">
+        <v>6418</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="I76" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J76" t="n">
+        <v>516</v>
+      </c>
+      <c r="K76" t="n">
+        <v>3</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>310</v>
+      </c>
+      <c r="N76" t="n">
+        <v>5</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>11436</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>10150</v>
+      </c>
+      <c r="R76" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S76" t="n">
+        <v>2156</v>
+      </c>
+      <c r="T76" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2797</v>
+      </c>
+      <c r="V76" t="n">
+        <v>27</v>
+      </c>
+      <c r="W76" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI76"/>
+  <dimension ref="A1:AI77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9392,6 +9392,124 @@
       <c r="AI76" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>16:44:47</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E77" t="n">
+        <v>243450</v>
+      </c>
+      <c r="F77" t="n">
+        <v>6416</v>
+      </c>
+      <c r="G77" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1.146</v>
+      </c>
+      <c r="I77" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J77" t="n">
+        <v>521</v>
+      </c>
+      <c r="K77" t="n">
+        <v>5</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>312</v>
+      </c>
+      <c r="N77" t="n">
+        <v>2</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>11591</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>10110</v>
+      </c>
+      <c r="R77" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S77" t="n">
+        <v>2199</v>
+      </c>
+      <c r="T77" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2824</v>
+      </c>
+      <c r="V77" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="W77" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>1/1</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI77"/>
+  <dimension ref="A1:AI78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9510,6 +9510,124 @@
       <c r="AI77" t="inlineStr">
         <is>
           <t>1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>16:45:59</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E78" t="n">
+        <v>243580</v>
+      </c>
+      <c r="F78" t="n">
+        <v>6416</v>
+      </c>
+      <c r="G78" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="I78" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J78" t="n">
+        <v>326</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-195</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>981</v>
+      </c>
+      <c r="N78" t="n">
+        <v>669</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>10856</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>10077</v>
+      </c>
+      <c r="R78" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S78" t="n">
+        <v>2197</v>
+      </c>
+      <c r="T78" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U78" t="n">
+        <v>2818</v>
+      </c>
+      <c r="V78" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="W78" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI78"/>
+  <dimension ref="A1:AI79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9626,6 +9626,124 @@
         </is>
       </c>
       <c r="AI78" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>16:47:11</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E79" t="n">
+        <v>243594</v>
+      </c>
+      <c r="F79" t="n">
+        <v>6417</v>
+      </c>
+      <c r="G79" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1.093</v>
+      </c>
+      <c r="I79" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J79" t="n">
+        <v>321</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>981</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>10898</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>9971</v>
+      </c>
+      <c r="R79" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S79" t="n">
+        <v>2174</v>
+      </c>
+      <c r="T79" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U79" t="n">
+        <v>2781</v>
+      </c>
+      <c r="V79" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="W79" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI79"/>
+  <dimension ref="A1:AI80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9744,6 +9744,118 @@
         </is>
       </c>
       <c r="AI79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>16:48:45</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E80" t="n">
+        <v>250749</v>
+      </c>
+      <c r="F80" t="n">
+        <v>7482</v>
+      </c>
+      <c r="G80" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="I80" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J80" t="n">
+        <v>322</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>983</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>10912</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>10084</v>
+      </c>
+      <c r="R80" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S80" t="n">
+        <v>2128</v>
+      </c>
+      <c r="T80" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U80" t="n">
+        <v>2945</v>
+      </c>
+      <c r="V80" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="W80" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI80"/>
+  <dimension ref="A1:AI81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9856,6 +9856,124 @@
         </is>
       </c>
       <c r="AI80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>16:49:52</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E81" t="n">
+        <v>250844</v>
+      </c>
+      <c r="F81" t="n">
+        <v>7480</v>
+      </c>
+      <c r="G81" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="I81" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J81" t="n">
+        <v>344</v>
+      </c>
+      <c r="K81" t="n">
+        <v>22</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>954</v>
+      </c>
+      <c r="N81" t="n">
+        <v>-29</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>10973</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>9953</v>
+      </c>
+      <c r="R81" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S81" t="n">
+        <v>2140</v>
+      </c>
+      <c r="T81" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U81" t="n">
+        <v>2936</v>
+      </c>
+      <c r="V81" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="W81" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI81"/>
+  <dimension ref="A1:AI82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9974,6 +9974,124 @@
         </is>
       </c>
       <c r="AI81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>16:51:02</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E82" t="n">
+        <v>250801</v>
+      </c>
+      <c r="F82" t="n">
+        <v>7476</v>
+      </c>
+      <c r="G82" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I82" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J82" t="n">
+        <v>340</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>958</v>
+      </c>
+      <c r="N82" t="n">
+        <v>4</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>10944</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>10038</v>
+      </c>
+      <c r="R82" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S82" t="n">
+        <v>2139</v>
+      </c>
+      <c r="T82" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U82" t="n">
+        <v>2967</v>
+      </c>
+      <c r="V82" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="W82" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI82"/>
+  <dimension ref="A1:AI83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10092,6 +10092,124 @@
         </is>
       </c>
       <c r="AI82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>16:52:13</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E83" t="n">
+        <v>250801</v>
+      </c>
+      <c r="F83" t="n">
+        <v>7489</v>
+      </c>
+      <c r="G83" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="I83" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J83" t="n">
+        <v>340</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>958</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>10924</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>9989</v>
+      </c>
+      <c r="R83" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S83" t="n">
+        <v>2140</v>
+      </c>
+      <c r="T83" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U83" t="n">
+        <v>2896</v>
+      </c>
+      <c r="V83" t="n">
+        <v>27</v>
+      </c>
+      <c r="W83" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI83"/>
+  <dimension ref="A1:AI84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10210,6 +10210,124 @@
         </is>
       </c>
       <c r="AI83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>16:53:26</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E84" t="n">
+        <v>250828</v>
+      </c>
+      <c r="F84" t="n">
+        <v>7492</v>
+      </c>
+      <c r="G84" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="I84" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J84" t="n">
+        <v>359</v>
+      </c>
+      <c r="K84" t="n">
+        <v>19</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>968</v>
+      </c>
+      <c r="N84" t="n">
+        <v>10</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>11006</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>9964</v>
+      </c>
+      <c r="R84" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S84" t="n">
+        <v>2180</v>
+      </c>
+      <c r="T84" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U84" t="n">
+        <v>2881</v>
+      </c>
+      <c r="V84" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="W84" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI84"/>
+  <dimension ref="A1:AI85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10328,6 +10328,124 @@
         </is>
       </c>
       <c r="AI84" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>16:56:00</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E85" t="n">
+        <v>250903</v>
+      </c>
+      <c r="F85" t="n">
+        <v>7492</v>
+      </c>
+      <c r="G85" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="I85" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J85" t="n">
+        <v>367</v>
+      </c>
+      <c r="K85" t="n">
+        <v>8</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>963</v>
+      </c>
+      <c r="N85" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>11098</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>9968</v>
+      </c>
+      <c r="R85" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S85" t="n">
+        <v>2208</v>
+      </c>
+      <c r="T85" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U85" t="n">
+        <v>2897</v>
+      </c>
+      <c r="V85" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="W85" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI85"/>
+  <dimension ref="A1:AI86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10446,6 +10446,124 @@
         </is>
       </c>
       <c r="AI85" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>16:57:13</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E86" t="n">
+        <v>250762</v>
+      </c>
+      <c r="F86" t="n">
+        <v>7493</v>
+      </c>
+      <c r="G86" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="I86" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J86" t="n">
+        <v>366</v>
+      </c>
+      <c r="K86" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>962</v>
+      </c>
+      <c r="N86" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>10912</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>10089</v>
+      </c>
+      <c r="R86" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S86" t="n">
+        <v>2181</v>
+      </c>
+      <c r="T86" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U86" t="n">
+        <v>2969</v>
+      </c>
+      <c r="V86" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="W86" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI86"/>
+  <dimension ref="A1:AI87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10564,6 +10564,124 @@
         </is>
       </c>
       <c r="AI86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>16:58:29</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E87" t="n">
+        <v>250700</v>
+      </c>
+      <c r="F87" t="n">
+        <v>7494</v>
+      </c>
+      <c r="G87" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="I87" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J87" t="n">
+        <v>347</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-19</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>928</v>
+      </c>
+      <c r="N87" t="n">
+        <v>-34</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>10618</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>9996</v>
+      </c>
+      <c r="R87" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S87" t="n">
+        <v>2145</v>
+      </c>
+      <c r="T87" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U87" t="n">
+        <v>2900</v>
+      </c>
+      <c r="V87" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="W87" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI87"/>
+  <dimension ref="A1:AI88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10682,6 +10682,124 @@
         </is>
       </c>
       <c r="AI87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>17:00:54</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E88" t="n">
+        <v>250834</v>
+      </c>
+      <c r="F88" t="n">
+        <v>7494</v>
+      </c>
+      <c r="G88" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="I88" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J88" t="n">
+        <v>357</v>
+      </c>
+      <c r="K88" t="n">
+        <v>10</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>922</v>
+      </c>
+      <c r="N88" t="n">
+        <v>-6</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>10671</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>9909</v>
+      </c>
+      <c r="R88" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S88" t="n">
+        <v>2164</v>
+      </c>
+      <c r="T88" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U88" t="n">
+        <v>2874</v>
+      </c>
+      <c r="V88" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="W88" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI88"/>
+  <dimension ref="A1:AI89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10800,6 +10800,124 @@
         </is>
       </c>
       <c r="AI88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>17:02:08</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E89" t="n">
+        <v>250700</v>
+      </c>
+      <c r="F89" t="n">
+        <v>7495</v>
+      </c>
+      <c r="G89" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="I89" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J89" t="n">
+        <v>363</v>
+      </c>
+      <c r="K89" t="n">
+        <v>6</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>945</v>
+      </c>
+      <c r="N89" t="n">
+        <v>23</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>10516</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>10048</v>
+      </c>
+      <c r="R89" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S89" t="n">
+        <v>2101</v>
+      </c>
+      <c r="T89" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U89" t="n">
+        <v>2887</v>
+      </c>
+      <c r="V89" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W89" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI89"/>
+  <dimension ref="A1:AI90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10918,6 +10918,118 @@
         </is>
       </c>
       <c r="AI89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>17:03:25</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E90" t="n">
+        <v>250640</v>
+      </c>
+      <c r="F90" t="n">
+        <v>7495</v>
+      </c>
+      <c r="G90" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="I90" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J90" t="n">
+        <v>363</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>970</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>10515</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>10093</v>
+      </c>
+      <c r="R90" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S90" t="n">
+        <v>2084</v>
+      </c>
+      <c r="T90" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U90" t="n">
+        <v>2873</v>
+      </c>
+      <c r="V90" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="W90" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI90"/>
+  <dimension ref="A1:AI91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11030,6 +11030,124 @@
         </is>
       </c>
       <c r="AI90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>17:04:32</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E91" t="n">
+        <v>250630</v>
+      </c>
+      <c r="F91" t="n">
+        <v>7494</v>
+      </c>
+      <c r="G91" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="I91" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J91" t="n">
+        <v>358</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>979</v>
+      </c>
+      <c r="N91" t="n">
+        <v>9</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>10504</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>10043</v>
+      </c>
+      <c r="R91" t="n">
+        <v>235000</v>
+      </c>
+      <c r="S91" t="n">
+        <v>2077</v>
+      </c>
+      <c r="T91" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U91" t="n">
+        <v>2837</v>
+      </c>
+      <c r="V91" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="W91" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>235000</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI91"/>
+  <dimension ref="A1:AI92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11148,6 +11148,118 @@
         </is>
       </c>
       <c r="AI91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>17:06:11</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E92" t="n">
+        <v>250630</v>
+      </c>
+      <c r="F92" t="n">
+        <v>7494</v>
+      </c>
+      <c r="G92" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1.055</v>
+      </c>
+      <c r="I92" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J92" t="n">
+        <v>366</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>972</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>10581</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>10028</v>
+      </c>
+      <c r="R92" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S92" t="n">
+        <v>2104</v>
+      </c>
+      <c r="T92" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U92" t="n">
+        <v>2834</v>
+      </c>
+      <c r="V92" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="W92" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI92"/>
+  <dimension ref="A1:AI93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11260,6 +11260,124 @@
         </is>
       </c>
       <c r="AI92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>17:07:16</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E93" t="n">
+        <v>250630</v>
+      </c>
+      <c r="F93" t="n">
+        <v>7491</v>
+      </c>
+      <c r="G93" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="H93" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="I93" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J93" t="n">
+        <v>356</v>
+      </c>
+      <c r="K93" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>974</v>
+      </c>
+      <c r="N93" t="n">
+        <v>2</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>10594</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>9967</v>
+      </c>
+      <c r="R93" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S93" t="n">
+        <v>2130</v>
+      </c>
+      <c r="T93" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U93" t="n">
+        <v>2820</v>
+      </c>
+      <c r="V93" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="W93" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI93"/>
+  <dimension ref="A1:AI94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11378,6 +11378,124 @@
         </is>
       </c>
       <c r="AI93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>17:08:28</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E94" t="n">
+        <v>250630</v>
+      </c>
+      <c r="F94" t="n">
+        <v>7491</v>
+      </c>
+      <c r="G94" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="I94" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J94" t="n">
+        <v>365</v>
+      </c>
+      <c r="K94" t="n">
+        <v>9</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>978</v>
+      </c>
+      <c r="N94" t="n">
+        <v>4</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>10536</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>10074</v>
+      </c>
+      <c r="R94" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S94" t="n">
+        <v>2129</v>
+      </c>
+      <c r="T94" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U94" t="n">
+        <v>2843</v>
+      </c>
+      <c r="V94" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="W94" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI94"/>
+  <dimension ref="A1:AI95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11496,6 +11496,124 @@
         </is>
       </c>
       <c r="AI94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>17:09:38</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E95" t="n">
+        <v>250630</v>
+      </c>
+      <c r="F95" t="n">
+        <v>7491</v>
+      </c>
+      <c r="G95" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="I95" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J95" t="n">
+        <v>366</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>971</v>
+      </c>
+      <c r="N95" t="n">
+        <v>-7</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>10450</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>10022</v>
+      </c>
+      <c r="R95" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S95" t="n">
+        <v>2111</v>
+      </c>
+      <c r="T95" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U95" t="n">
+        <v>2823</v>
+      </c>
+      <c r="V95" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="W95" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI95"/>
+  <dimension ref="A1:AI96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11614,6 +11614,124 @@
         </is>
       </c>
       <c r="AI95" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>17:10:50</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E96" t="n">
+        <v>250630</v>
+      </c>
+      <c r="F96" t="n">
+        <v>7490</v>
+      </c>
+      <c r="G96" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="I96" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J96" t="n">
+        <v>349</v>
+      </c>
+      <c r="K96" t="n">
+        <v>-17</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>978</v>
+      </c>
+      <c r="N96" t="n">
+        <v>7</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>10353</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>10037</v>
+      </c>
+      <c r="R96" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S96" t="n">
+        <v>2103</v>
+      </c>
+      <c r="T96" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U96" t="n">
+        <v>2810</v>
+      </c>
+      <c r="V96" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W96" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI96"/>
+  <dimension ref="A1:AI97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11732,6 +11732,124 @@
         </is>
       </c>
       <c r="AI96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>17:12:02</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E97" t="n">
+        <v>250628</v>
+      </c>
+      <c r="F97" t="n">
+        <v>7488</v>
+      </c>
+      <c r="G97" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="H97" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="I97" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J97" t="n">
+        <v>345</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>971</v>
+      </c>
+      <c r="N97" t="n">
+        <v>-7</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>10394</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>10040</v>
+      </c>
+      <c r="R97" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S97" t="n">
+        <v>2093</v>
+      </c>
+      <c r="T97" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U97" t="n">
+        <v>2804</v>
+      </c>
+      <c r="V97" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W97" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI97"/>
+  <dimension ref="A1:AI98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11850,6 +11850,124 @@
         </is>
       </c>
       <c r="AI97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>17:13:14</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E98" t="n">
+        <v>250628</v>
+      </c>
+      <c r="F98" t="n">
+        <v>7488</v>
+      </c>
+      <c r="G98" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="H98" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="I98" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J98" t="n">
+        <v>498</v>
+      </c>
+      <c r="K98" t="n">
+        <v>153</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
+        <v>316</v>
+      </c>
+      <c r="N98" t="n">
+        <v>-655</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>11126</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>10099</v>
+      </c>
+      <c r="R98" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S98" t="n">
+        <v>2080</v>
+      </c>
+      <c r="T98" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U98" t="n">
+        <v>2827</v>
+      </c>
+      <c r="V98" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="W98" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI98"/>
+  <dimension ref="A1:AI99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11968,6 +11968,124 @@
         </is>
       </c>
       <c r="AI98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>17:14:26</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E99" t="n">
+        <v>250550</v>
+      </c>
+      <c r="F99" t="n">
+        <v>7481</v>
+      </c>
+      <c r="G99" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="H99" t="n">
+        <v>1.039</v>
+      </c>
+      <c r="I99" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J99" t="n">
+        <v>347</v>
+      </c>
+      <c r="K99" t="n">
+        <v>-151</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>978</v>
+      </c>
+      <c r="N99" t="n">
+        <v>662</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>10417</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>10025</v>
+      </c>
+      <c r="R99" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S99" t="n">
+        <v>2096</v>
+      </c>
+      <c r="T99" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U99" t="n">
+        <v>2793</v>
+      </c>
+      <c r="V99" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W99" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI99"/>
+  <dimension ref="A1:AI100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12086,6 +12086,124 @@
         </is>
       </c>
       <c r="AI99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>17:15:38</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E100" t="n">
+        <v>250866</v>
+      </c>
+      <c r="F100" t="n">
+        <v>7459</v>
+      </c>
+      <c r="G100" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="H100" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="I100" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J100" t="n">
+        <v>353</v>
+      </c>
+      <c r="K100" t="n">
+        <v>6</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>954</v>
+      </c>
+      <c r="N100" t="n">
+        <v>-24</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>10559</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>9858</v>
+      </c>
+      <c r="R100" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S100" t="n">
+        <v>2146</v>
+      </c>
+      <c r="T100" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U100" t="n">
+        <v>2746</v>
+      </c>
+      <c r="V100" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W100" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI100"/>
+  <dimension ref="A1:AI101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12204,6 +12204,124 @@
         </is>
       </c>
       <c r="AI100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>17:16:51</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E101" t="n">
+        <v>250924</v>
+      </c>
+      <c r="F101" t="n">
+        <v>7461</v>
+      </c>
+      <c r="G101" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="H101" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="I101" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J101" t="n">
+        <v>372</v>
+      </c>
+      <c r="K101" t="n">
+        <v>19</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>887</v>
+      </c>
+      <c r="N101" t="n">
+        <v>-67</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>10648</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>9709</v>
+      </c>
+      <c r="R101" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S101" t="n">
+        <v>2125</v>
+      </c>
+      <c r="T101" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U101" t="n">
+        <v>2765</v>
+      </c>
+      <c r="V101" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="W101" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI101"/>
+  <dimension ref="A1:AI102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12322,6 +12322,124 @@
         </is>
       </c>
       <c r="AI101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>17:18:02</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E102" t="n">
+        <v>251006</v>
+      </c>
+      <c r="F102" t="n">
+        <v>7465</v>
+      </c>
+      <c r="G102" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="I102" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J102" t="n">
+        <v>377</v>
+      </c>
+      <c r="K102" t="n">
+        <v>5</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>868</v>
+      </c>
+      <c r="N102" t="n">
+        <v>-19</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>10683</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>9854</v>
+      </c>
+      <c r="R102" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S102" t="n">
+        <v>2125</v>
+      </c>
+      <c r="T102" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U102" t="n">
+        <v>2753</v>
+      </c>
+      <c r="V102" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W102" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI102"/>
+  <dimension ref="A1:AI103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12440,6 +12440,124 @@
         </is>
       </c>
       <c r="AI102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>17:20:26</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E103" t="n">
+        <v>250800</v>
+      </c>
+      <c r="F103" t="n">
+        <v>7470</v>
+      </c>
+      <c r="G103" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="H103" t="n">
+        <v>1.059</v>
+      </c>
+      <c r="I103" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J103" t="n">
+        <v>447</v>
+      </c>
+      <c r="K103" t="n">
+        <v>70</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M103" t="n">
+        <v>871</v>
+      </c>
+      <c r="N103" t="n">
+        <v>3</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>10580</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>9993</v>
+      </c>
+      <c r="R103" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S103" t="n">
+        <v>2124</v>
+      </c>
+      <c r="T103" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U103" t="n">
+        <v>2809</v>
+      </c>
+      <c r="V103" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W103" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI103"/>
+  <dimension ref="A1:AI104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12558,6 +12558,124 @@
         </is>
       </c>
       <c r="AI103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>17:21:37</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E104" t="n">
+        <v>250800</v>
+      </c>
+      <c r="F104" t="n">
+        <v>7470</v>
+      </c>
+      <c r="G104" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="H104" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="I104" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J104" t="n">
+        <v>453</v>
+      </c>
+      <c r="K104" t="n">
+        <v>6</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M104" t="n">
+        <v>858</v>
+      </c>
+      <c r="N104" t="n">
+        <v>-13</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>10602</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>9904</v>
+      </c>
+      <c r="R104" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S104" t="n">
+        <v>2117</v>
+      </c>
+      <c r="T104" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U104" t="n">
+        <v>2791</v>
+      </c>
+      <c r="V104" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="W104" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI104"/>
+  <dimension ref="A1:AI105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12676,6 +12676,124 @@
         </is>
       </c>
       <c r="AI104" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>17:22:50</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E105" t="n">
+        <v>250800</v>
+      </c>
+      <c r="F105" t="n">
+        <v>7470</v>
+      </c>
+      <c r="G105" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="H105" t="n">
+        <v>1.059</v>
+      </c>
+      <c r="I105" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J105" t="n">
+        <v>451</v>
+      </c>
+      <c r="K105" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>861</v>
+      </c>
+      <c r="N105" t="n">
+        <v>3</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>10539</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>9956</v>
+      </c>
+      <c r="R105" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S105" t="n">
+        <v>2114</v>
+      </c>
+      <c r="T105" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U105" t="n">
+        <v>2822</v>
+      </c>
+      <c r="V105" t="n">
+        <v>28</v>
+      </c>
+      <c r="W105" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI105"/>
+  <dimension ref="A1:AI106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12794,6 +12794,118 @@
         </is>
       </c>
       <c r="AI105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>17:24:08</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E106" t="n">
+        <v>250530</v>
+      </c>
+      <c r="F106" t="n">
+        <v>7468</v>
+      </c>
+      <c r="G106" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="H106" t="n">
+        <v>1.026</v>
+      </c>
+      <c r="I106" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J106" t="n">
+        <v>432</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>861</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>10312</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>10046</v>
+      </c>
+      <c r="R106" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S106" t="n">
+        <v>2096</v>
+      </c>
+      <c r="T106" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U106" t="n">
+        <v>2859</v>
+      </c>
+      <c r="V106" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="W106" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI106"/>
+  <dimension ref="A1:AI107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12906,6 +12906,124 @@
         </is>
       </c>
       <c r="AI106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>17:25:15</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E107" t="n">
+        <v>250530</v>
+      </c>
+      <c r="F107" t="n">
+        <v>7468</v>
+      </c>
+      <c r="G107" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="I107" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J107" t="n">
+        <v>429</v>
+      </c>
+      <c r="K107" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>862</v>
+      </c>
+      <c r="N107" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>10335</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>10050</v>
+      </c>
+      <c r="R107" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S107" t="n">
+        <v>2099</v>
+      </c>
+      <c r="T107" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U107" t="n">
+        <v>2828</v>
+      </c>
+      <c r="V107" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="W107" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI107"/>
+  <dimension ref="A1:AI108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13024,6 +13024,124 @@
         </is>
       </c>
       <c r="AI107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>17:26:26</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E108" t="n">
+        <v>250640</v>
+      </c>
+      <c r="F108" t="n">
+        <v>7468</v>
+      </c>
+      <c r="G108" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="H108" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="I108" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J108" t="n">
+        <v>490</v>
+      </c>
+      <c r="K108" t="n">
+        <v>61</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M108" t="n">
+        <v>308</v>
+      </c>
+      <c r="N108" t="n">
+        <v>-554</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>10814</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>10151</v>
+      </c>
+      <c r="R108" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S108" t="n">
+        <v>2036</v>
+      </c>
+      <c r="T108" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U108" t="n">
+        <v>2861</v>
+      </c>
+      <c r="V108" t="n">
+        <v>28</v>
+      </c>
+      <c r="W108" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI108"/>
+  <dimension ref="A1:AI109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13142,6 +13142,124 @@
         </is>
       </c>
       <c r="AI108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>17:27:32</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E109" t="n">
+        <v>250363</v>
+      </c>
+      <c r="F109" t="n">
+        <v>7472</v>
+      </c>
+      <c r="G109" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="H109" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="I109" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J109" t="n">
+        <v>491</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M109" t="n">
+        <v>309</v>
+      </c>
+      <c r="N109" t="n">
+        <v>1</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>10902</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>10193</v>
+      </c>
+      <c r="R109" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S109" t="n">
+        <v>2070</v>
+      </c>
+      <c r="T109" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U109" t="n">
+        <v>2877</v>
+      </c>
+      <c r="V109" t="n">
+        <v>28</v>
+      </c>
+      <c r="W109" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI109"/>
+  <dimension ref="A1:AI110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13260,6 +13260,124 @@
         </is>
       </c>
       <c r="AI109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>17:28:38</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E110" t="n">
+        <v>250632</v>
+      </c>
+      <c r="F110" t="n">
+        <v>7477</v>
+      </c>
+      <c r="G110" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="H110" t="n">
+        <v>1.085</v>
+      </c>
+      <c r="I110" t="n">
+        <v>243000</v>
+      </c>
+      <c r="J110" t="n">
+        <v>484</v>
+      </c>
+      <c r="K110" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M110" t="n">
+        <v>312</v>
+      </c>
+      <c r="N110" t="n">
+        <v>3</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>10978</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>10120</v>
+      </c>
+      <c r="R110" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S110" t="n">
+        <v>2133</v>
+      </c>
+      <c r="T110" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U110" t="n">
+        <v>2860</v>
+      </c>
+      <c r="V110" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="W110" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI110"/>
+  <dimension ref="A1:AI111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13378,6 +13378,124 @@
         </is>
       </c>
       <c r="AI110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>17:29:44</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E111" t="n">
+        <v>250521</v>
+      </c>
+      <c r="F111" t="n">
+        <v>7483</v>
+      </c>
+      <c r="G111" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1.026</v>
+      </c>
+      <c r="I111" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J111" t="n">
+        <v>375</v>
+      </c>
+      <c r="K111" t="n">
+        <v>-109</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M111" t="n">
+        <v>869</v>
+      </c>
+      <c r="N111" t="n">
+        <v>557</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>10376</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>10111</v>
+      </c>
+      <c r="R111" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S111" t="n">
+        <v>2175</v>
+      </c>
+      <c r="T111" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U111" t="n">
+        <v>2851</v>
+      </c>
+      <c r="V111" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="W111" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI111"/>
+  <dimension ref="A1:AI112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13496,6 +13496,124 @@
         </is>
       </c>
       <c r="AI111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>17:30:50</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E112" t="n">
+        <v>250729</v>
+      </c>
+      <c r="F112" t="n">
+        <v>7483</v>
+      </c>
+      <c r="G112" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H112" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I112" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J112" t="n">
+        <v>370</v>
+      </c>
+      <c r="K112" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M112" t="n">
+        <v>928</v>
+      </c>
+      <c r="N112" t="n">
+        <v>59</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>10323</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>10219</v>
+      </c>
+      <c r="R112" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S112" t="n">
+        <v>2155</v>
+      </c>
+      <c r="T112" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U112" t="n">
+        <v>2845</v>
+      </c>
+      <c r="V112" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W112" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI112"/>
+  <dimension ref="A1:AI113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13614,6 +13614,124 @@
         </is>
       </c>
       <c r="AI112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>17:31:55</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E113" t="n">
+        <v>250846</v>
+      </c>
+      <c r="F113" t="n">
+        <v>7483</v>
+      </c>
+      <c r="G113" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H113" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="I113" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J113" t="n">
+        <v>381</v>
+      </c>
+      <c r="K113" t="n">
+        <v>11</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M113" t="n">
+        <v>919</v>
+      </c>
+      <c r="N113" t="n">
+        <v>-9</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>10494</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>10054</v>
+      </c>
+      <c r="R113" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S113" t="n">
+        <v>2209</v>
+      </c>
+      <c r="T113" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U113" t="n">
+        <v>2847</v>
+      </c>
+      <c r="V113" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="W113" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/index_tracker_SILVER_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI113"/>
+  <dimension ref="A1:AI114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13732,6 +13732,124 @@
         </is>
       </c>
       <c r="AI113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>17:33:02</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E114" t="n">
+        <v>250898</v>
+      </c>
+      <c r="F114" t="n">
+        <v>7503</v>
+      </c>
+      <c r="G114" t="n">
+        <v>12</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="I114" t="n">
+        <v>244000</v>
+      </c>
+      <c r="J114" t="n">
+        <v>392</v>
+      </c>
+      <c r="K114" t="n">
+        <v>11</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M114" t="n">
+        <v>879</v>
+      </c>
+      <c r="N114" t="n">
+        <v>-40</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>10550</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>10075</v>
+      </c>
+      <c r="R114" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S114" t="n">
+        <v>2239</v>
+      </c>
+      <c r="T114" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U114" t="n">
+        <v>2920</v>
+      </c>
+      <c r="V114" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="W114" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
         <is>
           <t>—</t>
         </is>
